--- a/artfynd/S 872-2025 artfynd.xlsx
+++ b/artfynd/S 872-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2223,57 +2223,60 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124851977</v>
+        <v>135525936</v>
       </c>
       <c r="B15" t="n">
-        <v>58085</v>
+        <v>58139</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205976</v>
+        <v>103020</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Drakamöllan p-plats, Maglehem, Sk</t>
+          <t>Bäckholmen, Sk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445639</v>
+        <v>445650</v>
       </c>
       <c r="R15" t="n">
-        <v>6179581</v>
+        <v>6179552</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2297,22 +2300,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>06:04</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2327,27 +2330,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jörgen Sagvik</t>
+          <t>Sören  Uppsäll</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jörgen Sagvik</t>
+          <t>Sören  Uppsäll , Elisabeth Uppsäll, Karin Eskilson, Conny Eskilson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124851977</t>
+          <t>https://artportalen.se/Sighting/135525936</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>84848871</v>
+        <v>124851977</v>
       </c>
       <c r="B16" t="n">
-        <v>58826</v>
+        <v>58085</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,41 +2358,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208242</v>
+        <v>205976</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Drakamöllan, Sk</t>
+          <t>Drakamöllan p-plats, Maglehem, Sk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445423</v>
+        <v>445639</v>
       </c>
       <c r="R16" t="n">
-        <v>6179329</v>
+        <v>6179581</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2398,7 +2406,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Simrishamn</t>
+          <t>Tomelilla</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2408,27 +2416,27 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Ravlunda</t>
+          <t>Brösarp</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-04-25</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>06:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-04-25</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2443,27 +2451,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Klas Rådberg</t>
+          <t>Jörgen Sagvik</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Klas Rådberg</t>
+          <t>Jörgen Sagvik</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84848871</t>
+          <t>https://artportalen.se/Sighting/124851977</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>81366412</v>
+        <v>84848871</v>
       </c>
       <c r="B17" t="n">
-        <v>104808</v>
+        <v>58826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,37 +2479,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220464</v>
+        <v>208242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lundbräsma</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cardamine impatiens</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>SV Brostorp, Sk</t>
+          <t>Drakamöllan, Sk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446174</v>
+        <v>445423</v>
       </c>
       <c r="R17" t="n">
-        <v>6179439</v>
+        <v>6179329</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2525,12 +2537,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2008-05-03</t>
+          <t>2020-04-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2008-05-03</t>
+          <t>2020-04-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,57 +2563,48 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Klas Rådberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bengt Sandkull</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Skånes Flora Millora 2008-2015</t>
-        </is>
-      </c>
+          <t>Klas Rådberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81366412</t>
+          <t>https://artportalen.se/Sighting/84848871</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>81366280</v>
+        <v>81366412</v>
       </c>
       <c r="B18" t="n">
-        <v>106813</v>
+        <v>104808</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220785</v>
+        <v>220464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Lundbräsma</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cardamine impatiens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2676,33 +2689,33 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81366280</t>
+          <t>https://artportalen.se/Sighting/81366412</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>107832289</v>
+        <v>81366280</v>
       </c>
       <c r="B19" t="n">
-        <v>111019</v>
+        <v>106813</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222776</v>
+        <v>220785</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2711,23 +2724,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Drakamöllan 100 m S parkeringen, Sk</t>
+          <t>SV Brostorp, Sk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445646</v>
+        <v>446174</v>
       </c>
       <c r="R19" t="n">
-        <v>6179519</v>
+        <v>6179439</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2751,12 +2760,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-04-04</t>
+          <t>2008-05-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-04-04</t>
+          <t>2008-05-03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,77 +2774,84 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>lövskogsbryn</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Staffan Nilsson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Staffan Nilsson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Bengt Sandkull</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Skånes Flora Millora 2008-2015</t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107832289</t>
+          <t>https://artportalen.se/Sighting/81366280</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>81365942</v>
+        <v>107832289</v>
       </c>
       <c r="B20" t="n">
-        <v>103403</v>
+        <v>111019</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223246</v>
+        <v>222776</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>SV Brostorp, Sk</t>
+          <t>Drakamöllan 100 m S parkeringen, Sk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446174</v>
+        <v>445646</v>
       </c>
       <c r="R20" t="n">
-        <v>6179439</v>
+        <v>6179519</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2859,12 +2875,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2008-05-03</t>
+          <t>2023-04-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2008-05-03</t>
+          <t>2023-04-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,81 +2889,74 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>lövskogsbryn</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Staffan Nilsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Sandkull</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Skånes Flora Millora 2008-2015</t>
-        </is>
-      </c>
+          <t>Staffan Nilsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81365942</t>
+          <t>https://artportalen.se/Sighting/107832289</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>88869159</v>
+        <v>81365942</v>
       </c>
       <c r="B21" t="n">
-        <v>58327</v>
+        <v>103403</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>223246</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Glimmebodaskogen, Sk</t>
+          <t>SV Brostorp, Sk</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443938</v>
+        <v>446174</v>
       </c>
       <c r="R21" t="n">
-        <v>6178349</v>
+        <v>6179439</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2959,7 +2968,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Tomelilla</t>
+          <t>Simrishamn</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2969,17 +2978,17 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Brösarp</t>
+          <t>Ravlunda</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2020-11-03</t>
+          <t>2008-05-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2020-11-03</t>
+          <t>2008-05-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2990,31 +2999,40 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Bengt Sandkull</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Skånes Flora Millora 2008-2015</t>
+        </is>
+      </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88869159</t>
+          <t>https://artportalen.se/Sighting/81365942</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>556542</v>
+        <v>88869159</v>
       </c>
       <c r="B22" t="n">
-        <v>91137</v>
+        <v>58327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3022,37 +3040,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1541</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällsopp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Strobilomyces strobilaceus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Berk.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Maglehem - Ora, Sk</t>
+          <t>Glimmebodaskogen, Sk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445565</v>
+        <v>443938</v>
       </c>
       <c r="R22" t="n">
-        <v>6178111</v>
+        <v>6178349</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3061,7 +3083,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Simrishamn</t>
+          <t>Tomelilla</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -3071,22 +3093,17 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Ravlunda</t>
+          <t>Brösarp</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2007-09-22</t>
+          <t>2020-11-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2007-09-22</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bokskogsområde vid Ora - Maglehem. Områdte ligger i Ravlunda socken.</t>
+          <t>2020-11-03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3097,87 +3114,69 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Bokskogsområde vid Ora - Maglehem. Områdte ligger i Ravlunda socken.</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Via Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>VBSK fynddatabas</t>
-        </is>
-      </c>
+          <t>Ulf Gärdenfors</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/556542</t>
+          <t>https://artportalen.se/Sighting/88869159</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>95238028</v>
+        <v>556542</v>
       </c>
       <c r="B23" t="n">
-        <v>107042</v>
+        <v>91137</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1654</v>
+        <v>1541</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsveronika</t>
+          <t>Fjällsopp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Veronica montana</t>
+          <t>Strobilomyces strobilaceus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Berk.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gussaröd, 2,2 km OSO, Sk</t>
+          <t>Maglehem - Ora, Sk</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445723</v>
+        <v>445565</v>
       </c>
       <c r="R23" t="n">
-        <v>6178275</v>
+        <v>6178111</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3199,19 +3198,19 @@
           <t>Ravlunda</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>M-Sim-0656</t>
-        </is>
-      </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2007-09-22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2007-09-22</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Bokskogsområde vid Ora - Maglehem. Områdte ligger i Ravlunda socken.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3225,75 +3224,84 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>I kanten av markväg</t>
+          <t>Bokskogsområde vid Ora - Maglehem. Områdte ligger i Ravlunda socken.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
+          <t>Via Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>VBSK fynddatabas</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95238028</t>
+          <t>https://artportalen.se/Sighting/556542</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1135866</v>
+        <v>95238028</v>
       </c>
       <c r="B24" t="n">
-        <v>89823</v>
+        <v>107042</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2979</v>
+        <v>1654</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lömsk flugsvamp</t>
+          <t>Skogsveronika</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Amanita phalloides</t>
+          <t>Veronica montana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Link</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Maglehem - Ora, Sk</t>
+          <t>Gussaröd, 2,2 km OSO, Sk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445565</v>
+        <v>445723</v>
       </c>
       <c r="R24" t="n">
-        <v>6178111</v>
+        <v>6178275</v>
       </c>
       <c r="S24" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3315,19 +3323,19 @@
           <t>Ravlunda</t>
         </is>
       </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>M-Sim-0656</t>
+        </is>
+      </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2007-09-22</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2007-09-22</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bokskogsområde vid Ora - Maglehem. Områdte ligger i Ravlunda socken.</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3341,37 +3349,37 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Bokskogsområde vid Ora - Maglehem. Områdte ligger i Ravlunda socken.</t>
+          <t>I kanten av markväg</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Via Rolf-Göran Carlsson</t>
+          <t>Charlotte Wigermo, Åke Svensson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>VBSK fynddatabas</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1135866</t>
+          <t>https://artportalen.se/Sighting/95238028</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118909649</v>
+        <v>1135866</v>
       </c>
       <c r="B25" t="n">
-        <v>57947</v>
+        <v>89823</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,45 +3387,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102977</v>
+        <v>2979</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Lömsk flugsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Amanita phalloides</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Fr.:Fr.) Link</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Maglehems ora, Sk</t>
+          <t>Maglehem - Ora, Sk</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445526</v>
+        <v>445565</v>
       </c>
       <c r="R25" t="n">
-        <v>6177962</v>
+        <v>6178111</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3441,22 +3441,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>07:56</t>
+          <t>2007-09-22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>07:56</t>
+          <t>2007-09-22</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Bokskogsområde vid Ora - Maglehem. Områdte ligger i Ravlunda socken.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3467,48 +3462,57 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Bokskogsområde vid Ora - Maglehem. Områdte ligger i Ravlunda socken.</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Robin Mårtensson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Robin Mårtensson, Marcus Carlsson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Via Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>VBSK fynddatabas</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118909649</t>
+          <t>https://artportalen.se/Sighting/1135866</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>98532941</v>
+        <v>118909649</v>
       </c>
       <c r="B26" t="n">
-        <v>58393</v>
+        <v>57947</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102999</v>
+        <v>102977</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3518,22 +3522,26 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Maglehems Ora, Sk</t>
+          <t>Maglehems ora, Sk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445250</v>
+        <v>445526</v>
       </c>
       <c r="R26" t="n">
-        <v>6178094</v>
+        <v>6177962</v>
       </c>
       <c r="S26" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3557,12 +3565,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-02-09</t>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-02-09</t>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3577,68 +3595,69 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Robin Mårtensson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Robin Mårtensson, Marcus Carlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98532941</t>
+          <t>https://artportalen.se/Sighting/118909649</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129217944</v>
+        <v>98532941</v>
       </c>
       <c r="B27" t="n">
-        <v>91490</v>
+        <v>58393</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1068</v>
+        <v>102999</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten stinksvamp</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Mutinus caninus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.:Pers.) Fr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Dammåkravägen, Sk</t>
+          <t>Maglehems Ora, Sk</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446172</v>
+        <v>445250</v>
       </c>
       <c r="R27" t="n">
-        <v>6176815</v>
+        <v>6178094</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3662,12 +3681,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2022-02-09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2022-02-09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3676,69 +3695,71 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129217944</t>
+          <t>https://artportalen.se/Sighting/98532941</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126453171</v>
+        <v>129217944</v>
       </c>
       <c r="B28" t="n">
-        <v>41735</v>
+        <v>91490</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101256</v>
+        <v>1068</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre purpurmätare</t>
+          <t>Liten stinksvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lythria cruentaria</t>
+          <t>Mutinus caninus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1767)</t>
+          <t>(Schaeff.:Pers.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>ravlunda skjutfält, Sk</t>
+          <t>Dammåkravägen, Sk</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446145</v>
+        <v>446172</v>
       </c>
       <c r="R28" t="n">
-        <v>6176833</v>
+        <v>6176815</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3765,12 +3786,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3779,79 +3800,69 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Björkén</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Björkén</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126453171</t>
+          <t>https://artportalen.se/Sighting/129217944</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>93367378</v>
+        <v>126453171</v>
       </c>
       <c r="B29" t="n">
-        <v>56876</v>
+        <v>41735</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>208257</v>
+        <v>101256</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Mindre purpurmätare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Lythria cruentaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+          <t>(Hufnagel, 1767)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ravlunda, Sk</t>
+          <t>ravlunda skjutfält, Sk</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445916</v>
+        <v>446145</v>
       </c>
       <c r="R29" t="n">
-        <v>6176901</v>
+        <v>6176833</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3878,22 +3889,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>16:02</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>16:02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3908,16 +3909,139 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Anders Björkén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Anders Björkén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126453171</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>93367378</v>
+      </c>
+      <c r="B30" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ravlunda, Sk</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>445916</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6176901</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Simrishamn</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ravlunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/93367378</t>
         </is>
@@ -3953,6 +4077,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 872-2025 artfynd.xlsx
+++ b/artfynd/S 872-2025 artfynd.xlsx
@@ -2226,7 +2226,7 @@
         <v>135525936</v>
       </c>
       <c r="B15" t="n">
-        <v>58139</v>
+        <v>58141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
